--- a/Employee_Reports_wi48/Romie Ross Tamayo Eleosida Q0605.xlsx
+++ b/Employee_Reports_wi48/Romie Ross Tamayo Eleosida Q0605.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1279,9 +1279,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
           <t>29-Jan-2026</t>
@@ -1293,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1342,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1379,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1416,11 +1428,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1465,11 +1477,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1502,11 +1514,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1964,7 +1976,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7945</v>
+        <v>7942</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2059,7 +2071,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2088,7 +2100,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2117,7 +2129,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2146,7 +2158,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7937</v>
+        <v>7934</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2175,7 +2187,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2216,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7940</v>
+        <v>7937</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2233,7 +2245,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7946</v>
+        <v>7943</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2262,7 +2274,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2303,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2320,7 +2332,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2349,7 +2361,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2378,7 +2390,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2419,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
